--- a/Doc/导出配置/Random.xlsx
+++ b/Doc/导出配置/Random.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A1F04D-5612-4F77-891F-CFA8C4C2A841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{104DF018-02E7-4A11-83BE-BDB9D0779F94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="715" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Random" sheetId="13" r:id="rId1"/>
@@ -20,17 +20,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">随机辅助!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{5EBE70D3-C295-4A26-BE5A-DD67CB396847}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{EDEDC7A6-FCC2-4ECD-8C9F-B628188BB70F}">
       <text>
         <r>
           <rPr>
@@ -52,7 +52,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{144E4CF1-DBAA-42C5-BABC-AFCA1681FCD0}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{755AE2FE-90E4-4B01-B8B3-EF5884A91F28}">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{94E76A40-914D-49FF-B29E-ACE1644051BA}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{C2D9410C-5B26-4FE0-8D44-D6D18ED0C811}">
       <text>
         <r>
           <rPr>
@@ -112,10 +112,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>毛俭铭</author>
+    <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{5D1182CD-6C0F-4153-B551-DE48460ACF24}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{B0794C45-2E68-4D15-B118-784A61AAC168}">
       <text>
         <r>
           <rPr>
@@ -142,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{79CF57B9-E850-4B84-9BD3-0F212CF09635}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{33EAEEED-B990-41A4-B079-B3D29F5B35AA}">
       <text>
         <r>
           <rPr>
@@ -169,7 +169,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{83FDEED8-535F-4FE1-AC35-DD6845FC624E}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{BBC19200-B37B-4F4D-B0A5-4B69B4D551F8}">
       <text>
         <r>
           <rPr>
@@ -191,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{64EC1269-93DC-4B0E-B9D6-FBD5DFD595BC}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{AD8419E2-736E-4947-94F2-FD53B0A583BA}">
       <text>
         <r>
           <rPr>
@@ -213,7 +213,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{8858F3C4-7222-44E0-BCF7-5C7EDF9B6526}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{EBCC1407-722E-469A-B063-BFB464E1445E}">
       <text>
         <r>
           <rPr>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>索引</t>
   </si>
@@ -292,7 +292,11 @@
     <t>属性</t>
   </si>
   <si>
-    <t>生命</t>
+    <t>示例</t>
+  </si>
+  <si>
+    <t>当前经验</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -765,32 +769,26 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Cfg_Random" displayName="Cfg_Random" ref="A1:D5" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="索引" dataDxfId="11">
-      <calculatedColumnFormula>#REF!</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="10">
-      <calculatedColumnFormula>58*10^5+#REF!*100+#REF!</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="索引" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="掉率模式" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="掉落配置" dataDxfId="8">
-      <calculatedColumnFormula>"掉落辅助.行标签["&amp;Cfg_Random[[#This Row],[索引]]&amp;"]"</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="掉落配置" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="随机辅助" displayName="随机辅助" ref="A1:F8" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="随机辅助" displayName="随机辅助" ref="A1:F5" totalsRowShown="0">
   <tableColumns count="6">
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="分组" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="类型" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="ID" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="数量下限" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="数量上限" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="分组" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="类型" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="ID" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="数量下限" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="数量上限" dataDxfId="4">
       <calculatedColumnFormula>随机辅助[[#This Row],[数量下限]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="权重" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="权重" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1122,16 +1120,16 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.75" style="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="37.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="37.875" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1153,7 +1151,7 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1161,7 +1159,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1169,9 +1167,9 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1">
         <v>101</v>
@@ -1215,21 +1213,21 @@
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.21875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.25" style="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="15.44140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="10.88671875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -1249,7 +1247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1259,7 +1257,7 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -1269,7 +1267,7 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -1279,70 +1277,31 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="1">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1">
-        <v>10</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1">
-        <v>10</v>
-      </c>
-      <c r="E7" s="1">
-        <v>10</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1">
-        <v>10</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2000</v>
+      </c>
+      <c r="E5" s="1">
+        <f>随机辅助[[#This Row],[数量下限]]</f>
+        <v>2000</v>
+      </c>
+      <c r="F5" s="1">
         <v>10000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B8" xr:uid="{F7FF86F6-E090-40BC-94D0-D487198687A4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B5" xr:uid="{F7FF86F6-E090-40BC-94D0-D487198687A4}">
       <formula1>"随机组,属性"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1358,9 +1317,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB766472-2D7F-42EA-8222-368D602C859F}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1">
         <f>SUM(,)</f>
         <v>0</v>
@@ -1382,12 +1341,12 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="5">
         <v>36925</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" t="str">
         <f>DOLLAR(1,0)</f>
         <v>¥1</v>
@@ -1401,7 +1360,7 @@
         <v>1,000,000,000,000,000,000,000</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" t="e">
         <f ca="1">FIELDVALUE(1, "abc")</f>
         <v>#NAME?</v>
